--- a/功能清单模版.xlsx
+++ b/功能清单模版.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="176">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="175">
   <si>
     <t>项目名称</t>
   </si>
@@ -249,10 +249,10 @@
     <t>管理端</t>
   </si>
   <si>
-    <t>数据采集与清洗</t>
-  </si>
-  <si>
-    <t>批量导入Excel文件，进行去重，格式统一并入库</t>
+    <t>数据异构导入</t>
+  </si>
+  <si>
+    <t>批量导入异构Excel文件，进行去重，格式统一并入库，支持自定义模板保存</t>
   </si>
   <si>
     <t>职位元数据管理</t>
@@ -264,22 +264,22 @@
     <t>类似苍穹外卖的菜品管理</t>
   </si>
   <si>
-    <t>角色-权限管理</t>
-  </si>
-  <si>
-    <t>创建角色，分配权限</t>
-  </si>
-  <si>
-    <t>用户-角色管理</t>
-  </si>
-  <si>
-    <t>给用户分配角色</t>
+    <t>角色管理</t>
+  </si>
+  <si>
+    <t>创建角色，给用户分配角色</t>
+  </si>
+  <si>
+    <t>资源管理</t>
+  </si>
+  <si>
+    <t>将权限资源分配给角色</t>
   </si>
   <si>
     <t>智能匹配</t>
   </si>
   <si>
-    <t>多维精准筛查</t>
+    <t>岗位筛查</t>
   </si>
   <si>
     <t>用户根据专业，学历，政治面貌，应届身份等维度进行过滤</t>
@@ -339,13 +339,10 @@
     <t>用户可收藏心仪岗位，并在报名截止前收到系统提醒</t>
   </si>
   <si>
-    <t>类似“购物车”但无支付</t>
-  </si>
-  <si>
-    <t>百科检索</t>
-  </si>
-  <si>
-    <t>集成考公/考研常识问答，支持全文搜索（可以接入本地知识库）</t>
+    <t>异常处理与测试</t>
+  </si>
+  <si>
+    <t>建立全局异常处理器，完整日志，单元测试，API测试，核心功能完整测试</t>
   </si>
   <si>
     <t>开发详细计划</t>
@@ -3340,7 +3337,7 @@
       <tableStyleElement type="firstRowStripe" dxfId="1"/>
       <tableStyleElement type="firstColumnStripe" dxfId="0"/>
     </tableStyle>
-    <tableStyle name="MySqlDefault" pivot="0" table="0" count="2" xr9:uid="{D3CE4A0A-4AD5-44C9-B54E-FF53051434CC}">
+    <tableStyle name="MySqlDefault" pivot="0" table="0" count="2" xr9:uid="{10B82558-7720-4030-A238-9ACB4409FDB2}">
       <tableStyleElement type="wholeTable" dxfId="8"/>
       <tableStyleElement type="headerRow" dxfId="7"/>
     </tableStyle>
@@ -4523,149 +4520,123 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="59"/>
-      <c r="B9" s="64"/>
-      <c r="C9" s="63"/>
-      <c r="D9" s="63"/>
-      <c r="E9" s="59"/>
+      <c r="B9" s="64" t="s">
+        <v>76</v>
+      </c>
+      <c r="C9" s="63" t="s">
+        <v>77</v>
+      </c>
+      <c r="D9" s="63" t="s">
+        <v>78</v>
+      </c>
+      <c r="E9" s="59" t="s">
+        <v>79</v>
+      </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="59"/>
       <c r="B10" s="64"/>
-      <c r="C10" s="63"/>
-      <c r="D10" s="63"/>
-      <c r="E10" s="59"/>
+      <c r="C10" s="63" t="s">
+        <v>80</v>
+      </c>
+      <c r="D10" s="63" t="s">
+        <v>81</v>
+      </c>
+      <c r="E10" s="59" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="59"/>
-      <c r="B11" s="64"/>
-      <c r="C11" s="63"/>
-      <c r="D11" s="63"/>
-      <c r="E11" s="59"/>
+      <c r="B11" s="64" t="s">
+        <v>83</v>
+      </c>
+      <c r="C11" s="63" t="s">
+        <v>84</v>
+      </c>
+      <c r="D11" s="63" t="s">
+        <v>85</v>
+      </c>
+      <c r="E11" s="59" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="59"/>
-      <c r="B12" s="64"/>
-      <c r="C12" s="63"/>
-      <c r="D12" s="63"/>
+      <c r="B12" s="65"/>
+      <c r="C12" s="63" t="s">
+        <v>87</v>
+      </c>
+      <c r="D12" s="63" t="s">
+        <v>88</v>
+      </c>
       <c r="E12" s="59"/>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="59"/>
-      <c r="B13" s="64"/>
-      <c r="C13" s="63"/>
-      <c r="D13" s="63"/>
+      <c r="B13" s="58" t="s">
+        <v>89</v>
+      </c>
+      <c r="C13" s="59" t="s">
+        <v>90</v>
+      </c>
+      <c r="D13" s="59" t="s">
+        <v>91</v>
+      </c>
       <c r="E13" s="59"/>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="59"/>
-      <c r="B14" s="64"/>
-      <c r="C14" s="63"/>
-      <c r="D14" s="63"/>
+      <c r="B14" s="61"/>
+      <c r="C14" s="59" t="s">
+        <v>92</v>
+      </c>
+      <c r="D14" s="59" t="s">
+        <v>93</v>
+      </c>
       <c r="E14" s="59"/>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="59"/>
-      <c r="B15" s="64" t="s">
-        <v>76</v>
-      </c>
-      <c r="C15" s="63" t="s">
-        <v>77</v>
-      </c>
-      <c r="D15" s="63" t="s">
-        <v>78</v>
-      </c>
-      <c r="E15" s="59" t="s">
-        <v>79</v>
-      </c>
+      <c r="B15" s="58" t="s">
+        <v>94</v>
+      </c>
+      <c r="C15" s="59" t="s">
+        <v>95</v>
+      </c>
+      <c r="D15" s="59" t="s">
+        <v>96</v>
+      </c>
+      <c r="E15" s="59"/>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="59"/>
-      <c r="B16" s="64"/>
-      <c r="C16" s="63" t="s">
-        <v>80</v>
-      </c>
-      <c r="D16" s="63" t="s">
-        <v>81</v>
-      </c>
-      <c r="E16" s="59" t="s">
-        <v>82</v>
-      </c>
+      <c r="B16" s="61"/>
+      <c r="C16" s="59" t="s">
+        <v>97</v>
+      </c>
+      <c r="D16" s="59" t="s">
+        <v>98</v>
+      </c>
+      <c r="E16" s="59"/>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="59"/>
-      <c r="B17" s="64" t="s">
-        <v>83</v>
-      </c>
-      <c r="C17" s="63" t="s">
-        <v>84</v>
-      </c>
-      <c r="D17" s="63" t="s">
-        <v>85</v>
-      </c>
-      <c r="E17" s="59" t="s">
-        <v>86</v>
-      </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="59"/>
-      <c r="B18" s="65"/>
-      <c r="C18" s="63" t="s">
-        <v>87</v>
-      </c>
-      <c r="D18" s="63" t="s">
-        <v>88</v>
-      </c>
-      <c r="E18" s="59"/>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="59"/>
-      <c r="B19" s="58" t="s">
-        <v>89</v>
-      </c>
-      <c r="C19" s="59" t="s">
-        <v>90</v>
-      </c>
-      <c r="D19" s="59" t="s">
-        <v>91</v>
-      </c>
-      <c r="E19" s="59"/>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="59"/>
-      <c r="B20" s="61"/>
-      <c r="C20" s="59" t="s">
-        <v>92</v>
-      </c>
-      <c r="D20" s="59" t="s">
-        <v>93</v>
-      </c>
-      <c r="E20" s="59"/>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="59"/>
-      <c r="B21" s="58" t="s">
-        <v>94</v>
-      </c>
-      <c r="C21" s="59" t="s">
-        <v>95</v>
-      </c>
-      <c r="D21" s="59" t="s">
-        <v>96</v>
-      </c>
-      <c r="E21" s="59" t="s">
-        <v>97</v>
-      </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="59"/>
-      <c r="B22" s="61"/>
-      <c r="C22" s="59" t="s">
-        <v>98</v>
-      </c>
-      <c r="D22" s="59" t="s">
-        <v>99</v>
-      </c>
-      <c r="E22" s="59"/>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="59"/>
@@ -5145,11 +5116,11 @@
   </sheetData>
   <mergeCells count="6">
     <mergeCell ref="B2:B4"/>
-    <mergeCell ref="B5:B7"/>
+    <mergeCell ref="B5:B8"/>
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="B13:B14"/>
     <mergeCell ref="B15:B16"/>
-    <mergeCell ref="B17:B18"/>
-    <mergeCell ref="B19:B20"/>
-    <mergeCell ref="B21:B22"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
@@ -5184,7 +5155,7 @@
   <sheetData>
     <row r="1" s="1" customFormat="1" ht="30" customHeight="1" spans="2:15">
       <c r="B1" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C1" s="3"/>
       <c r="D1" s="3"/>
@@ -5200,43 +5171,43 @@
     <row r="3" ht="8.25" customHeight="1"/>
     <row r="5" customFormat="1" ht="30" spans="2:15">
       <c r="B5" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="C5" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="D5" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="E5" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="F5" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="F5" s="5" t="s">
+      <c r="G5" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="G5" s="5" t="s">
+      <c r="H5" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="H5" s="5" t="s">
+      <c r="I5" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="I5" s="5" t="s">
+      <c r="J5" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="J5" s="5" t="s">
+      <c r="K5" s="5" t="s">
         <v>109</v>
       </c>
-      <c r="K5" s="5" t="s">
+      <c r="L5" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="L5" s="5" t="s">
+      <c r="M5" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="M5" s="5" t="s">
+      <c r="N5" s="5" t="s">
         <v>112</v>
-      </c>
-      <c r="N5" s="5" t="s">
-        <v>113</v>
       </c>
       <c r="O5" s="5" t="s">
         <v>58</v>
@@ -5244,16 +5215,16 @@
     </row>
     <row r="6" customFormat="1" ht="14" spans="2:15">
       <c r="B6" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="C6" s="7" t="s">
         <v>114</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="D6" s="8" t="s">
         <v>115</v>
       </c>
-      <c r="D6" s="8" t="s">
+      <c r="E6" s="9" t="s">
         <v>116</v>
-      </c>
-      <c r="E6" s="9" t="s">
-        <v>117</v>
       </c>
       <c r="F6" s="10"/>
       <c r="G6" s="10"/>
@@ -5286,10 +5257,10 @@
       <c r="B8" s="13"/>
       <c r="C8" s="14"/>
       <c r="D8" s="17" t="s">
+        <v>117</v>
+      </c>
+      <c r="E8" s="18" t="s">
         <v>118</v>
-      </c>
-      <c r="E8" s="18" t="s">
-        <v>119</v>
       </c>
       <c r="F8" s="19"/>
       <c r="G8" s="20"/>
@@ -5337,13 +5308,13 @@
     <row r="11" customFormat="1" ht="14" spans="2:15">
       <c r="B11" s="13"/>
       <c r="C11" s="27" t="s">
+        <v>119</v>
+      </c>
+      <c r="D11" s="17" t="s">
         <v>120</v>
       </c>
-      <c r="D11" s="17" t="s">
+      <c r="E11" s="28" t="s">
         <v>121</v>
-      </c>
-      <c r="E11" s="28" t="s">
-        <v>122</v>
       </c>
       <c r="F11" s="19"/>
       <c r="G11" s="20"/>
@@ -5361,7 +5332,7 @@
       <c r="C12" s="29"/>
       <c r="D12" s="25"/>
       <c r="E12" s="28" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="F12" s="19"/>
       <c r="G12" s="20"/>
@@ -5378,10 +5349,10 @@
       <c r="B13" s="13"/>
       <c r="C13" s="29"/>
       <c r="D13" s="17" t="s">
+        <v>123</v>
+      </c>
+      <c r="E13" s="18" t="s">
         <v>124</v>
-      </c>
-      <c r="E13" s="18" t="s">
-        <v>125</v>
       </c>
       <c r="F13" s="19"/>
       <c r="G13" s="20"/>
@@ -5399,7 +5370,7 @@
       <c r="C14" s="29"/>
       <c r="D14" s="25"/>
       <c r="E14" s="30" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F14" s="31"/>
       <c r="G14" s="20"/>
@@ -5419,7 +5390,7 @@
         <v>83</v>
       </c>
       <c r="E15" s="30" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F15" s="31"/>
       <c r="G15" s="20"/>
@@ -5437,7 +5408,7 @@
       <c r="C16" s="29"/>
       <c r="D16" s="25"/>
       <c r="E16" s="32" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F16" s="31"/>
       <c r="G16" s="20"/>
@@ -5454,10 +5425,10 @@
       <c r="B17" s="13"/>
       <c r="C17" s="29"/>
       <c r="D17" s="33" t="s">
+        <v>128</v>
+      </c>
+      <c r="E17" s="34" t="s">
         <v>129</v>
-      </c>
-      <c r="E17" s="34" t="s">
-        <v>130</v>
       </c>
       <c r="F17" s="31"/>
       <c r="G17" s="20"/>
@@ -5475,7 +5446,7 @@
       <c r="C18" s="35"/>
       <c r="D18" s="33"/>
       <c r="E18" s="36" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F18" s="31"/>
       <c r="G18" s="20"/>
@@ -5491,13 +5462,13 @@
     <row r="19" customFormat="1" ht="14" spans="2:16">
       <c r="B19" s="13"/>
       <c r="C19" s="27" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D19" s="33" t="s">
         <v>89</v>
       </c>
       <c r="E19" s="26" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F19" s="19"/>
       <c r="G19" s="20"/>
@@ -5515,7 +5486,7 @@
       <c r="C20" s="29"/>
       <c r="D20" s="33"/>
       <c r="E20" s="28" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F20" s="19"/>
       <c r="G20" s="20"/>
@@ -5535,7 +5506,7 @@
         <v>94</v>
       </c>
       <c r="E21" s="37" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F21" s="19"/>
       <c r="G21" s="20"/>
@@ -5553,7 +5524,7 @@
       <c r="C22" s="35"/>
       <c r="D22" s="33"/>
       <c r="E22" s="37" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F22" s="19"/>
       <c r="G22" s="20"/>
@@ -5569,13 +5540,13 @@
     <row r="23" customFormat="1" ht="13.95" customHeight="1" spans="2:16">
       <c r="B23" s="13"/>
       <c r="C23" s="38" t="s">
+        <v>136</v>
+      </c>
+      <c r="D23" s="39" t="s">
         <v>137</v>
       </c>
-      <c r="D23" s="39" t="s">
+      <c r="E23" s="40" t="s">
         <v>138</v>
-      </c>
-      <c r="E23" s="40" t="s">
-        <v>139</v>
       </c>
       <c r="F23" s="19"/>
       <c r="G23" s="20"/>
@@ -5592,10 +5563,10 @@
       <c r="B24" s="13"/>
       <c r="C24" s="41"/>
       <c r="D24" s="42" t="s">
+        <v>139</v>
+      </c>
+      <c r="E24" s="43" t="s">
         <v>140</v>
-      </c>
-      <c r="E24" s="43" t="s">
-        <v>141</v>
       </c>
       <c r="F24" s="19"/>
       <c r="G24" s="20"/>
@@ -5613,7 +5584,7 @@
       <c r="C25" s="41"/>
       <c r="D25" s="44"/>
       <c r="E25" s="45" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F25" s="31"/>
       <c r="G25" s="20"/>
@@ -5631,10 +5602,10 @@
       <c r="B26" s="13"/>
       <c r="C26" s="41"/>
       <c r="D26" s="39" t="s">
+        <v>142</v>
+      </c>
+      <c r="E26" s="46" t="s">
         <v>143</v>
-      </c>
-      <c r="E26" s="46" t="s">
-        <v>144</v>
       </c>
       <c r="F26" s="19"/>
       <c r="G26" s="20"/>
@@ -5652,7 +5623,7 @@
       <c r="C27" s="41"/>
       <c r="D27" s="39"/>
       <c r="E27" s="47" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F27" s="19"/>
       <c r="G27" s="20"/>
@@ -5669,10 +5640,10 @@
       <c r="B28" s="13"/>
       <c r="C28" s="41"/>
       <c r="D28" s="39" t="s">
+        <v>145</v>
+      </c>
+      <c r="E28" s="47" t="s">
         <v>146</v>
-      </c>
-      <c r="E28" s="47" t="s">
-        <v>147</v>
       </c>
       <c r="F28" s="19"/>
       <c r="G28" s="20"/>
@@ -5689,10 +5660,10 @@
       <c r="B29" s="13"/>
       <c r="C29" s="41"/>
       <c r="D29" s="39" t="s">
+        <v>147</v>
+      </c>
+      <c r="E29" s="47" t="s">
         <v>148</v>
-      </c>
-      <c r="E29" s="47" t="s">
-        <v>149</v>
       </c>
       <c r="F29" s="19"/>
       <c r="G29" s="20"/>
@@ -5709,10 +5680,10 @@
       <c r="B30" s="13"/>
       <c r="C30" s="41"/>
       <c r="D30" s="39" t="s">
+        <v>149</v>
+      </c>
+      <c r="E30" s="47" t="s">
         <v>150</v>
-      </c>
-      <c r="E30" s="47" t="s">
-        <v>151</v>
       </c>
       <c r="F30" s="19"/>
       <c r="G30" s="20"/>
@@ -5729,10 +5700,10 @@
       <c r="B31" s="13"/>
       <c r="C31" s="48"/>
       <c r="D31" s="39" t="s">
+        <v>151</v>
+      </c>
+      <c r="E31" s="47" t="s">
         <v>152</v>
-      </c>
-      <c r="E31" s="47" t="s">
-        <v>153</v>
       </c>
       <c r="F31" s="19"/>
       <c r="G31" s="20"/>
@@ -5748,13 +5719,13 @@
     <row r="32" customFormat="1" ht="14" spans="2:16">
       <c r="B32" s="13"/>
       <c r="C32" s="38" t="s">
+        <v>153</v>
+      </c>
+      <c r="D32" s="49" t="s">
         <v>154</v>
       </c>
-      <c r="D32" s="49" t="s">
+      <c r="E32" s="26" t="s">
         <v>155</v>
-      </c>
-      <c r="E32" s="26" t="s">
-        <v>156</v>
       </c>
       <c r="F32" s="19"/>
       <c r="G32" s="20"/>
@@ -5771,10 +5742,10 @@
       <c r="B33" s="13"/>
       <c r="C33" s="41"/>
       <c r="D33" s="50" t="s">
+        <v>156</v>
+      </c>
+      <c r="E33" s="28" t="s">
         <v>157</v>
-      </c>
-      <c r="E33" s="28" t="s">
-        <v>158</v>
       </c>
       <c r="F33" s="19"/>
       <c r="G33" s="20"/>
@@ -5791,10 +5762,10 @@
       <c r="B34" s="13"/>
       <c r="C34" s="41"/>
       <c r="D34" s="50" t="s">
+        <v>158</v>
+      </c>
+      <c r="E34" s="28" t="s">
         <v>159</v>
-      </c>
-      <c r="E34" s="28" t="s">
-        <v>160</v>
       </c>
       <c r="F34" s="19"/>
       <c r="G34" s="20"/>
@@ -5811,10 +5782,10 @@
       <c r="B35" s="13"/>
       <c r="C35" s="48"/>
       <c r="D35" s="50" t="s">
+        <v>160</v>
+      </c>
+      <c r="E35" s="28" t="s">
         <v>161</v>
-      </c>
-      <c r="E35" s="28" t="s">
-        <v>162</v>
       </c>
       <c r="F35" s="19"/>
       <c r="G35" s="20"/>
@@ -5830,13 +5801,13 @@
     <row r="36" customFormat="1" ht="14" spans="2:15">
       <c r="B36" s="13"/>
       <c r="C36" s="51" t="s">
+        <v>162</v>
+      </c>
+      <c r="D36" s="50" t="s">
         <v>163</v>
       </c>
-      <c r="D36" s="50" t="s">
+      <c r="E36" s="28" t="s">
         <v>164</v>
-      </c>
-      <c r="E36" s="28" t="s">
-        <v>165</v>
       </c>
       <c r="F36" s="19"/>
       <c r="G36" s="20"/>
@@ -5853,10 +5824,10 @@
       <c r="B37" s="13"/>
       <c r="C37" s="52"/>
       <c r="D37" s="50" t="s">
+        <v>165</v>
+      </c>
+      <c r="E37" s="21" t="s">
         <v>166</v>
-      </c>
-      <c r="E37" s="21" t="s">
-        <v>167</v>
       </c>
       <c r="F37" s="19"/>
       <c r="G37" s="20"/>
@@ -5874,7 +5845,7 @@
       <c r="C38" s="52"/>
       <c r="D38" s="50"/>
       <c r="E38" s="28" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="F38" s="19"/>
       <c r="G38" s="20"/>
@@ -5891,10 +5862,10 @@
       <c r="B39" s="13"/>
       <c r="C39" s="52"/>
       <c r="D39" s="50" t="s">
+        <v>168</v>
+      </c>
+      <c r="E39" s="28" t="s">
         <v>169</v>
-      </c>
-      <c r="E39" s="28" t="s">
-        <v>170</v>
       </c>
       <c r="F39" s="19"/>
       <c r="G39" s="20"/>
@@ -5911,10 +5882,10 @@
       <c r="B40" s="13"/>
       <c r="C40" s="53"/>
       <c r="D40" s="50" t="s">
+        <v>170</v>
+      </c>
+      <c r="E40" s="54" t="s">
         <v>171</v>
-      </c>
-      <c r="E40" s="54" t="s">
-        <v>172</v>
       </c>
       <c r="F40" s="19"/>
       <c r="G40" s="20"/>
@@ -5930,13 +5901,13 @@
     <row r="41" customFormat="1" ht="14" spans="2:15">
       <c r="B41" s="13"/>
       <c r="C41" s="55" t="s">
+        <v>172</v>
+      </c>
+      <c r="D41" s="50" t="s">
         <v>173</v>
       </c>
-      <c r="D41" s="50" t="s">
+      <c r="E41" s="54" t="s">
         <v>174</v>
-      </c>
-      <c r="E41" s="54" t="s">
-        <v>175</v>
       </c>
       <c r="F41" s="19"/>
       <c r="G41" s="20"/>
